--- a/RecetasId.xlsx
+++ b/RecetasId.xlsx
@@ -29,13 +29,13 @@
     <t>Usuario Registra</t>
   </si>
   <si>
-    <t>Lasaña</t>
+    <t>Suministro</t>
   </si>
   <si>
-    <t>13/10/2024 11:44:55 p. m.</t>
+    <t>09/10/2024 05:24:50 a. m.</t>
   </si>
   <si>
-    <t>Mabell</t>
+    <t>VGarcia</t>
   </si>
 </sst>
 </file>
@@ -109,13 +109,13 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>6</v>

--- a/RecetasId.xlsx
+++ b/RecetasId.xlsx
@@ -29,13 +29,13 @@
     <t>Usuario Registra</t>
   </si>
   <si>
-    <t>Suministro</t>
+    <t>PRUEBAPROYECTO</t>
   </si>
   <si>
-    <t>09/10/2024 05:24:50 a. m.</t>
+    <t>04/12/2024 02:56:55 p. m.</t>
   </si>
   <si>
-    <t>VGarcia</t>
+    <t>Mabell</t>
   </si>
 </sst>
 </file>
@@ -109,13 +109,13 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>6</v>
